--- a/data/vendor-search/results_all_lighting.xlsx
+++ b/data/vendor-search/results_all_lighting.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,6 +492,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_bsb002_firmware:1707040932:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_bsb002:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,6 +572,11 @@
           <t>cpe:2.3:o:philips:taolight_smart_wi-fi_wiz_connected_led_bulb_9290022656_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:philips:taolight_smart_wi-fi_wiz_connected_led_bulb_9290022656:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>wiz connected</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -592,6 +612,11 @@
           <t>cpe:2.3:o:ikea:tradfri_led1732g11_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:ikea:tradfri_led1732g11:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>tradfri</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -627,6 +652,11 @@
           <t>cpe:2.3:o:ikea:tradfri_gateway_e1526_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ikea:tradfri_gateway_e1526:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>tradfri</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -662,6 +692,11 @@
           <t>cpe:2.3:o:sengled:es21-n1eaw_firmware:0x0000024:*:*:*:*:*:*:*|cpe:2.3:h:sengled:es21-n1eaw:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>sengled</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -697,6 +732,11 @@
           <t>cpe:2.3:o:tapo:mini_smart_wi-fi_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:tapo:mini_smart_wi-fi_plug:-:*:*:*:*:*:*:*|cpe:2.3:o:nanoleaf:lightstrip_firmware:3.5.10:*:*:*:*:*:*:*|cpe:2.3:h:nanoleaf:lightstrip:-:*:*:*:*:*:*:*|cpe:2.3:o:govee:led_strip_firmware:3.00.42:*:*:*:*:*:*:*|cpe:2.3:h:govee:led_strip:-:*:*:*:*:*:*:*|cpe:2.3:o:switchbot:hub2_firmware:1.0-0.8:*:*:*:*:*:*:*|cpe:2.3:h:switchbot:hub2:-:*:*:*:*:*:*:*|cpe:2.3:o:phillips:hue_bridge_firmware:1.59.1959097030:*:*:*:*:*:*:*|cpe:2.3:h:phillips:hue_bridge:-:*:*:*:*:*:*:*|cpe:2.3:o:yeelight:smart_lamp_firmware:1.12.69:*:*:*:*:*:*:*|cpe:2.3:h:yeelight:smart_lamp:-:*:*:*:*:*:*:*|cpe:2.3:o:tp-link:smart_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:smart_plug:-:*:*:*:*:*:*:*|cpe:2.3:o:orein:smart_bulb_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:orein:smart_bulb:-:*:*:*:*:*:*:*|cpe:2.3:o:eve:eve_door_and_window_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:eve:eve_door_and_window:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>nanoleaf|yeelight</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -732,6 +772,11 @@
           <t>cpe:2.3:o:yeelight:smart_ai_speaker_firmware:3.3.10_0074:*:*:*:*:*:*:*|cpe:2.3:h:yeelight:smart_ai_speaker:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>yeelight</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -767,6 +812,11 @@
           <t>cpe:2.3:o:philips:hue_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -802,6 +852,11 @@
           <t>cpe:2.3:a:nanoleaf:nanoleaf_desktop:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>nanoleaf</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -837,6 +892,11 @@
           <t>cpe:2.3:o:sengled:e1e-g7f_firmware:0.0.9:*:*:*:*:*:*:*|cpe:2.3:h:sengled:e1e-g7f:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>sengled</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -872,6 +932,11 @@
           <t>cpe:2.3:o:nanoleaf:nanoleaf_firmware:7.1.1:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>nanoleaf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -907,6 +972,11 @@
           <t>cpe:2.3:o:nanoleaf:lightstrip_firmware:3.5.10:*:*:*:*:*:*:*|cpe:2.3:h:nanoleaf:lightstrip:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>nanoleaf</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -942,6 +1012,11 @@
           <t>cpe:2.3:a:yeelight:yeelight_classic:*:*:*:*:*:android:*:*</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>yeelight</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -977,6 +1052,11 @@
           <t>cpe:2.3:a:signify:wiz_connected:1.9.1:*:*:*:*:android:*:*</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>wiz connected</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1013,6 +1093,11 @@
           <t>cpe:2.3:a:razer:synapse:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1044,6 +1129,11 @@
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>nanoleaf</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1080,6 +1170,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1116,6 +1211,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1152,6 +1252,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1188,6 +1293,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1224,6 +1334,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1260,6 +1375,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1296,6 +1416,11 @@
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>philips hue</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1330,6 +1455,11 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>cpe:2.3:o:philips:hue_bridge_v2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:philips:hue_bridge_v2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>philips hue</t>
         </is>
       </c>
     </row>
